--- a/input_sceinarios_2.xlsx
+++ b/input_sceinarios_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2408975\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7F6B7EE-06A4-4D99-B325-8684D28332D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DF01C9-55C3-44D5-9E3A-00199CA0F002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{88BB600D-3B28-4A54-8732-C5E8B27BEA12}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Trace ID</t>
   </si>
@@ -54,67 +54,13 @@
   </si>
   <si>
     <t>I need to send 3 boxes of Fresh Mangoes from Seattle to Dallas. Each box weighs around 20 kg, with height, length, and width of 80 cm. It’s a type of food. Please deliver it by 2026-09-15.</t>
-  </si>
-  <si>
-    <t>019c6a10-6f73-7d30-9f33-eaf6e6c9c4bc</t>
-  </si>
-  <si>
-    <t>Please arrange the transportation of 8 boxes of Japanese Vase from BOSTON to Seattle. Each box weighs 15 kg and measures 120 cm in height, length, and width. The items are fragile and must be delivered by 2027-03-10.</t>
-  </si>
-  <si>
-    <t>019c75a0-2790-72f2-bd7e-4ada0410eca6</t>
-  </si>
-  <si>
-    <t>Please arrange the transportation of 4 boxes of Glass Lamps from Chicago to Denver. Each box weighs 12 kg and measures 90 cm in height, length, and width. The items are fragile and must be delivered by 2027-01-25.</t>
-  </si>
-  <si>
-    <t>019c6a1c-f9f6-7d80-987b-260479504188</t>
-  </si>
-  <si>
-    <t>Shipment request: office stationery(normal goods), 6 boxes x 12kg each, box dimentions 80x80x80 cm. Origin: Chicago. Destination: BOSTON. Required delivery date 2027-02-05.</t>
-  </si>
-  <si>
-    <t>019c75b2-ace8-7a61-8f1b-32df936adf4d</t>
-  </si>
-  <si>
-    <t>Shipment request: office supplies (normal goods), 5 boxes × 10 kg each, box dimensions 70 × 70 × 70 cm. Origin: BOSTON. Destination: Seattle. Required delivery date 2027-01-20</t>
-  </si>
-  <si>
-    <t>019c6a2b-1de1-7b01-bef8-9ac3ef97a291</t>
-  </si>
-  <si>
-    <t>Please coordinate the delivery of 6 boxes of fish from Seattle to BOSTON. Each box weighs 12kg and has dimensions of 80cm in height,length and width. The shipment consists of frozen goods and must be delivered by 2027-09-22</t>
-  </si>
-  <si>
-    <t>019c75c2-5f29-7270-8b7e-6b87c2581c54</t>
-  </si>
-  <si>
-    <t>Please coordinate the delivery of 4 boxes of frozen shrimp from New York to Chicago. Each box weighs 10 kg and has dimensions of 70 cm in height, length, and width. The shipment consists of frozen goods and must be delivered by 2027-08-10.</t>
-  </si>
-  <si>
-    <t>019c6a48-778d-7072-a115-9ad1edde9c5b</t>
-  </si>
-  <si>
-    <t>How many vendors are there in San Diego, I want the details in the following format: Vendor ID, Vendor Name, Capacity</t>
-  </si>
-  <si>
-    <t>019c6a4c-ad23-7b10-be47-8aeac3dc0344</t>
-  </si>
-  <si>
-    <t>Can you fetch me the status of the order with ID KX5687</t>
-  </si>
-  <si>
-    <t>019c6a4f-6a23-7c00-b75c-c290177d8bc4</t>
-  </si>
-  <si>
-    <t>Can you fetch me the performance of vendor 4001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,12 +73,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -161,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -171,7 +111,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,10 +445,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382F4238-D29D-46F1-88A6-81C7BA5774C3}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="362.5">
+    <row r="2" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -525,84 +464,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="362.5">
+    <row r="3" spans="1:2" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="409.5">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="333.5">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="333.5">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="409.5">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="409.5">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="232">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="101.5">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
